--- a/reconcile/storage/output/bruegel_investment_monitor.xlsx
+++ b/reconcile/storage/output/bruegel_investment_monitor.xlsx
@@ -4092,7 +4092,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4115,21 +4115,29 @@
           <t>2022-11</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2028-02</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.electrive.com/2025/02/24/calb-prepares-to-build-its-battery-plant-in-portugal/</t>
+          <t>https://autonews.gasgoo.com/new_energy/70036071.html?utm_source=openai</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://www.electrive.com/2025/02/24/calb-prepares-to-build-its-battery-plant-in-portugal/</t>
+          <t>https://autonews.gasgoo.com/new_energy/70036071.html?utm_source=openai</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://www.electrive.com/2025/02/24/calb-prepares-to-build-its-battery-plant-in-portugal/</t>
+          <t>https://autonews.gasgoo.com/new_energy/70036071.html?utm_source=openai</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4137,7 +4145,11 @@
           <t>https://www.electrive.com/2022/11/04/calb-signs-mou-for-factory-in-portugal/</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>https://autonews.gasgoo.com/new_energy/70036071.html?utm_source=openai</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
@@ -5985,12 +5997,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2028-03</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6015,7 +6027,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>https://www.electrive.com/2023/08/02/finnish-minerals-plans-cathode-materials-production/</t>
+          <t>https://www.electrive.com/2025/03/20/finnish-minerals-beijing-easpring-to-build-cam-plant-in-finland/</t>
         </is>
       </c>
       <c r="U63" t="inlineStr"/>

--- a/reconcile/storage/output/bruegel_investment_monitor.xlsx
+++ b/reconcile/storage/output/bruegel_investment_monitor.xlsx
@@ -16026,7 +16026,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ae solar</t>
+          <t>ae solar horizon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plovdiv</t>
+          <t>Kyustendil</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16064,46 +16064,46 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>150000000</v>
+        <v>10225994</v>
       </c>
       <c r="K3" t="n">
-        <v>150000000</v>
+        <v>10225994</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/ae-solar-to-build-solar-panel-plant-in-bulgaria/</t>
+          <t>https://balkangreenenergynews.com/ae-solar-horizon-to-produce-solar-panels-in-bulgaria/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/ae-solar-to-build-solar-panel-plant-in-bulgaria/</t>
+          <t>https://balkangreenenergynews.com/ae-solar-horizon-to-produce-solar-panels-in-bulgaria/</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/ae-solar-to-build-solar-panel-plant-in-bulgaria/</t>
+          <t>https://balkangreenenergynews.com/ae-solar-horizon-to-produce-solar-panels-in-bulgaria/</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/ae-solar-to-build-solar-panel-plant-in-bulgaria/</t>
+          <t>https://balkangreenenergynews.com/ae-solar-horizon-to-produce-solar-panels-in-bulgaria/</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>968c31c5-95af-5142-9693-d0f4c962e40e</t>
+          <t>2208907b-cd6a-5d6b-a9e2-dbb140fb9e62</t>
         </is>
       </c>
     </row>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kyustendil</t>
+          <t>Plovdiv</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16148,46 +16148,46 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>10225994</v>
+        <v>150000000</v>
       </c>
       <c r="K4" t="n">
-        <v>10225994</v>
+        <v>150000000</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/ae-solar-horizon-to-produce-solar-panels-in-bulgaria/</t>
+          <t>https://balkangreenenergynews.com/ae-solar-to-build-solar-panel-plant-in-bulgaria/</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/ae-solar-horizon-to-produce-solar-panels-in-bulgaria/</t>
+          <t>https://balkangreenenergynews.com/ae-solar-to-build-solar-panel-plant-in-bulgaria/</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/ae-solar-horizon-to-produce-solar-panels-in-bulgaria/</t>
+          <t>https://balkangreenenergynews.com/ae-solar-to-build-solar-panel-plant-in-bulgaria/</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/ae-solar-horizon-to-produce-solar-panels-in-bulgaria/</t>
+          <t>https://balkangreenenergynews.com/ae-solar-to-build-solar-panel-plant-in-bulgaria/</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2208907b-cd6a-5d6b-a9e2-dbb140fb9e62</t>
+          <t>0a5b74b7-ed35-55b7-a629-3cae1fe4eb9f</t>
         </is>
       </c>
     </row>
@@ -16370,17 +16370,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aleo sunrise</t>
+          <t>astrasun</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prenzlau</t>
+          <t>Teleorman County</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>cell, ingot_wafer, module</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -16398,71 +16398,63 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>13400000</v>
+        <v>102000000</v>
       </c>
       <c r="K7" t="n">
-        <v>13400000</v>
+        <v>102000000</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2013-09</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2013-09</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2016-09</t>
-        </is>
-      </c>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://www.pv-tech.org/aleo-sunrise-starts-perc-solar-cell-production-in-prenzlau-germany/</t>
+          <t>https://www.pv-magazine.com/2022/05/20/romania-to-host-integrated-ingot-cell-pv-module-production/</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://www.pv-tech.org/aleo-sunrise-starts-perc-solar-cell-production-in-prenzlau-germany/</t>
+          <t>https://www.pv-magazine.com/2022/05/20/romania-to-host-integrated-ingot-cell-pv-module-production/</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://www.pv-tech.org/aleo-sunrise-starts-perc-solar-cell-production-in-prenzlau-germany/</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
+          <t>https://www.pv-magazine.com/2022/05/20/romania-to-host-integrated-ingot-cell-pv-module-production/</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2022/05/20/romania-to-host-integrated-ingot-cell-pv-module-production/</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>https://www.pv-tech.org/aleo-sunrise-starts-perc-solar-cell-production-in-prenzlau-germany/</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>bb9a190f-c8b8-5f10-af69-c5502dcab55f</t>
+          <t>e97f7785-6b45-50f3-8965-1bdde09f6178</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>astrasun solar kft</t>
+          <t>astrasun</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -16486,7 +16478,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -16494,16 +16486,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>102000000</v>
+        <v>8000000</v>
       </c>
       <c r="K8" t="n">
-        <v>102000000</v>
+        <v>110000000</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -16539,24 +16531,24 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1cebf71c-5e6a-5387-b7de-82db790b9321</t>
+          <t>e97f7785-6b45-50f3-8965-1bdde09f6178</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>atersa</t>
+          <t>astrasun</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Teleorman County</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -16566,72 +16558,64 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>cell, module</t>
+          <t>cell, ingot_wafer, module</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.12</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>9960000</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>9960000</v>
+        <v>55000000</v>
       </c>
       <c r="L9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2009-08</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2009-08</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2012-08</t>
-        </is>
-      </c>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://www.glassglobal.com/profile/atersa_aplicaciones_t%C3%A9cnicas_de_la_energia_sl-57132.html</t>
+          <t>https://www.pv-magazine.com/2022/05/20/romania-to-host-integrated-ingot-cell-pv-module-production/</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://www.glassglobal.com/profile/atersa_aplicaciones_t%C3%A9cnicas_de_la_energia_sl-57132.html</t>
+          <t>https://www.pv-magazine.com/2022/05/20/romania-to-host-integrated-ingot-cell-pv-module-production/</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://www.glassglobal.com/profile/atersa_aplicaciones_t%C3%A9cnicas_de_la_energia_sl-57132.html</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
+          <t>https://www.pv-magazine.com/2022/05/20/romania-to-host-integrated-ingot-cell-pv-module-production/</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2022/05/20/romania-to-host-integrated-ingot-cell-pv-module-production/</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://www.grupoelecnor.com/news/the-regional-government-of-valencias-minister-of-economy-industry-and-trade-visits-atersas-facilities#:~:text=production%20capacity%20of%20154%20megawatt%20hours%20per%20year</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1fd091af-d4f3-56a1-b219-5c44f62a92e8</t>
+          <t>e97f7785-6b45-50f3-8965-1bdde09f6178</t>
         </is>
       </c>
     </row>
@@ -16662,57 +16646,65 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.224</v>
+        <v>0.12</v>
       </c>
       <c r="I10" t="n">
-        <v>0.344</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>18592000</v>
+        <v>9960000</v>
       </c>
       <c r="K10" t="n">
-        <v>28552000</v>
+        <v>9960000</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://www.devex.com/organizations/atersa-28710#:~:text=production%20capacity%20of%20344%20MW%20is%20planned</t>
+          <t>https://www.glassglobal.com/profile/atersa_aplicaciones_t%C3%A9cnicas_de_la_energia_sl-57132.html</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://www.devex.com/organizations/atersa-28710#:~:text=production%20capacity%20of%20344%20MW%20is%20planned</t>
+          <t>https://www.glassglobal.com/profile/atersa_aplicaciones_t%C3%A9cnicas_de_la_energia_sl-57132.html</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://www.devex.com/organizations/atersa-28710#:~:text=production%20capacity%20of%20344%20MW%20is%20planned</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>https://www.devex.com/organizations/atersa-28710#:~:text=production%20capacity%20of%20344%20MW%20is%20planned</t>
-        </is>
-      </c>
+          <t>https://www.glassglobal.com/profile/atersa_aplicaciones_t%C3%A9cnicas_de_la_energia_sl-57132.html</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://www.grupoelecnor.com/news/the-regional-government-of-valencias-minister-of-economy-industry-and-trade-visits-atersas-facilities#:~:text=production%20capacity%20of%20154%20megawatt%20hours%20per%20year</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>1fd091af-d4f3-56a1-b219-5c44f62a92e8</t>
@@ -16722,7 +16714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>atersa group</t>
+          <t>atersa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -16732,7 +16724,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Almussafes</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -16742,25 +16734,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>cell, module</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.344</v>
+        <v>0.224</v>
       </c>
       <c r="I11" t="n">
         <v>0.344</v>
       </c>
       <c r="J11" t="n">
-        <v>28552000</v>
+        <v>18592000</v>
       </c>
       <c r="K11" t="n">
         <v>28552000</v>
@@ -16770,51 +16762,43 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2022-07</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2022-07</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.energias-renovables.com/fotovoltaica/eclipse-solar-en-europa-20250703</t>
+          <t>https://www.devex.com/organizations/atersa-28710#:~:text=production%20capacity%20of%20344%20MW%20is%20planned</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://www.energias-renovables.com/fotovoltaica/eclipse-solar-en-europa-20250703</t>
+          <t>https://www.devex.com/organizations/atersa-28710#:~:text=production%20capacity%20of%20344%20MW%20is%20planned</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://www.energias-renovables.com/fotovoltaica/eclipse-solar-en-europa-20250703</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
+          <t>https://www.devex.com/organizations/atersa-28710#:~:text=production%20capacity%20of%20344%20MW%20is%20planned</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>https://www.devex.com/organizations/atersa-28710#:~:text=production%20capacity%20of%20344%20MW%20is%20planned</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://www.energias-renovables.com/fotovoltaica/eclipse-solar-en-europa-20250703</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>f3926aa4-fbc3-566f-9d25-6cbb515c3bca</t>
+          <t>1fd091af-d4f3-56a1-b219-5c44f62a92e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aurinka</t>
+          <t>atersa group</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -16824,7 +16808,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Almussafes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -16846,16 +16830,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.075</v>
+        <v>0.344</v>
       </c>
       <c r="I12" t="n">
-        <v>0.075</v>
+        <v>0.344</v>
       </c>
       <c r="J12" t="n">
-        <v>6225000</v>
+        <v>28552000</v>
       </c>
       <c r="K12" t="n">
-        <v>6225000</v>
+        <v>28552000</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -16899,7 +16883,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>4f7a59a5-341b-573a-bd88-5010d998de9a</t>
+          <t>f3926aa4-fbc3-566f-9d25-6cbb515c3bca</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16900,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Puertollano</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16938,16 +16922,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.3</v>
+        <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>0.075</v>
       </c>
       <c r="J13" t="n">
-        <v>24900000</v>
+        <v>6225000</v>
       </c>
       <c r="K13" t="n">
-        <v>24900000</v>
+        <v>6225000</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -16991,7 +16975,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>32a4ca61-e64d-51ae-9e5a-4824e777793b</t>
+          <t>4f7a59a5-341b-573a-bd88-5010d998de9a</t>
         </is>
       </c>
     </row>
@@ -17474,16 +17458,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="J19" t="n">
-        <v>9960000</v>
+        <v>2490000</v>
       </c>
       <c r="K19" t="n">
-        <v>9960000</v>
+        <v>2490000</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
@@ -17534,17 +17518,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>carbon</t>
+          <t>bruk bet solar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fos-sur-Mer</t>
+          <t>Tarnów</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17554,11 +17538,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>cell, ingot_wafer, module</t>
+          <t>module</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -17566,60 +17550,60 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.5</v>
+        <v>0.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="J20" t="n">
-        <v>41500000</v>
+        <v>7470000</v>
       </c>
       <c r="K20" t="n">
-        <v>41500000</v>
+        <v>9960000</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.world-energy.org/article/51711.html</t>
+          <t>https://www.pv-magazine.com/2017/06/06/polish-module-maker-bruk-bet-solar-raises-annual-capacity-to-120-mw/</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>https://www.world-energy.org/article/51711.html</t>
+          <t>https://www.pv-magazine.com/2017/06/06/polish-module-maker-bruk-bet-solar-raises-annual-capacity-to-120-mw/</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://www.world-energy.org/article/51711.html</t>
+          <t>https://www.pv-magazine.com/2017/06/06/polish-module-maker-bruk-bet-solar-raises-annual-capacity-to-120-mw/</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://www.world-energy.org/article/51711.html</t>
+          <t>https://www.pv-magazine.com/2017/06/06/polish-module-maker-bruk-bet-solar-raises-annual-capacity-to-120-mw/</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>04845c13-9fbc-5c9f-9096-21d9b5097cf7</t>
+          <t>ef53897e-dd73-5eeb-96b0-354cd3e31656</t>
         </is>
       </c>
     </row>
@@ -17650,43 +17634,43 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>under construction</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1658500000</v>
+        <v>41500000</v>
       </c>
       <c r="K21" t="n">
-        <v>1700000000</v>
+        <v>41500000</v>
       </c>
       <c r="L21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2028-05</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>https://www.world-energy.org/article/51711.html</t>
@@ -17699,20 +17683,16 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/09/23/carbon-acquires-photowatt/</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine.com/2023/03/06/french-manufacturer-chooses-5-gw-solar-factory-site/</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
           <t>https://www.world-energy.org/article/51711.html</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://www.world-energy.org/article/51711.html</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
           <t>04845c13-9fbc-5c9f-9096-21d9b5097cf7</t>
@@ -17746,21 +17726,21 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>under construction</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>under construction</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>1.5</v>
-      </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1658500000</v>
       </c>
       <c r="K22" t="n">
         <v>1700000000</v>
@@ -17818,17 +17798,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>comal</t>
+          <t>carbon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>L'Aquila</t>
+          <t>Fos-sur-Mer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17838,11 +17818,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>cell, ingot_wafer, module</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -17850,64 +17830,64 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>16100000</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>16100000</v>
+        <v>1700000000</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2027-07</t>
+          <t>2028-05</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/author/sergiomatalucci/</t>
+          <t>https://www.world-energy.org/article/51711.html</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/author/sergiomatalucci/</t>
+          <t>https://www.world-energy.org/article/51711.html</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://taiyangnews.info/markets/italian-epc-company-venturing-into-pv-manufacturing</t>
+          <t>https://www.pv-magazine.com/2024/09/23/carbon-acquires-photowatt/</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://taiyangnews.info/markets/italian-epc-company-venturing-into-pv-manufacturing</t>
+          <t>https://www.pv-magazine.com/2023/03/06/french-manufacturer-chooses-5-gw-solar-factory-site/</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/category/manufacturing/modules-upstream-manufacturing/page/5/</t>
+          <t>https://www.world-energy.org/article/51711.html</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>c692751f-bc73-5378-8d2c-9c32f3b64555</t>
+          <t>04845c13-9fbc-5c9f-9096-21d9b5097cf7</t>
         </is>
       </c>
     </row>
@@ -17924,7 +17904,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valsamoggia</t>
+          <t>L'Aquila</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -17952,24 +17932,24 @@
         <v>0.5</v>
       </c>
       <c r="J24" t="n">
-        <v>41500000</v>
+        <v>16100000</v>
       </c>
       <c r="K24" t="n">
-        <v>41500000</v>
+        <v>16100000</v>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>2024-07</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>2027-07</t>
@@ -17977,50 +17957,50 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
+          <t>https://www.pv-magazine.com/author/sergiomatalucci/</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
+          <t>https://www.pv-magazine.com/author/sergiomatalucci/</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
+          <t>https://www.energy-box.com/post/500-mw-solar-factory-site-purchased-by-comal-in-italy</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
+          <t>https://taiyangnews.info/markets/italian-epc-company-venturing-into-pv-manufacturing</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
+          <t>https://www.pv-magazine.com/category/manufacturing/modules-upstream-manufacturing/page/5/</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>a7d0f545-ad44-5cb7-b0ea-90c068c3671f</t>
+          <t>c692751f-bc73-5378-8d2c-9c32f3b64555</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>das solar</t>
+          <t>comal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mandeure</t>
+          <t>Valsamoggia</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -18038,63 +18018,75 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
-        <v>109000000</v>
+        <v>41500000</v>
       </c>
       <c r="K25" t="n">
-        <v>109000000</v>
+        <v>41500000</v>
       </c>
       <c r="L25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2027-07</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/author/gwenaelledeboutte/</t>
+          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/11/19/das-solar-to-build-3-gw-solar-module-factory-in-france/</t>
+          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/author/gwenaelledeboutte/</t>
+          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/11/19/das-solar-to-build-3-gw-solar-module-factory-in-france/</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2024/07/25/comal-plans-500-mw-solar-module-factory-in-italy/</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>095611ed-d1d1-5c64-974a-f040a638948b</t>
+          <t>a7d0f545-ad44-5cb7-b0ea-90c068c3671f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dracula technologies</t>
+          <t>das solar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -18104,7 +18096,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valence</t>
+          <t>Mandeure</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -18122,72 +18114,56 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.0007</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0007</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>15000000</v>
+        <v>109000000</v>
       </c>
       <c r="K26" t="n">
-        <v>15000000</v>
+        <v>109000000</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
+          <t>https://www.pv-magazine.com/author/gwenaelledeboutte/</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
+          <t>https://www.pv-magazine.com/2024/11/19/das-solar-to-build-3-gw-solar-module-factory-in-france/</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2023/10/19/dracula-technologies-builds-organic-pv-module-factory-in-france/</t>
+          <t>https://www.pv-magazine.com/author/gwenaelledeboutte/</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2023/10/19/dracula-technologies-builds-organic-pv-module-factory-in-france/</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine.com/2023/10/19/dracula-technologies-builds-organic-pv-module-factory-in-france/</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine.com/2023/10/19/dracula-technologies-builds-organic-pv-module-factory-in-france/</t>
-        </is>
-      </c>
+          <t>https://www.pv-magazine.com/2024/11/19/das-solar-to-build-3-gw-solar-module-factory-in-france/</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>ab958d6c-804b-53ec-8cc8-6b601343ee48</t>
+          <t>095611ed-d1d1-5c64-974a-f040a638948b</t>
         </is>
       </c>
     </row>
@@ -18218,35 +18194,43 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.0018</v>
+        <v>0.0007</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0025</v>
+        <v>0.0007</v>
       </c>
       <c r="J27" t="n">
-        <v>38571428.57142857</v>
+        <v>15000000</v>
       </c>
       <c r="K27" t="n">
-        <v>53571428.57142857</v>
+        <v>15000000</v>
       </c>
       <c r="L27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
@@ -18259,16 +18243,24 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
+          <t>https://www.pv-magazine.com/2023/10/19/dracula-technologies-builds-organic-pv-module-factory-in-france/</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+          <t>https://www.pv-magazine.com/2023/10/19/dracula-technologies-builds-organic-pv-module-factory-in-france/</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2023/10/19/dracula-technologies-builds-organic-pv-module-factory-in-france/</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2023/10/19/dracula-technologies-builds-organic-pv-module-factory-in-france/</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr">
         <is>
           <t>ab958d6c-804b-53ec-8cc8-6b601343ee48</t>
@@ -18278,17 +18270,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ecosolifer</t>
+          <t>dracula technologies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Győr-Moson-Sopron</t>
+          <t>Valence</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -18298,97 +18290,81 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>cell, module</t>
+          <t>module</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>announced</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>0.0018</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1</v>
+        <v>0.0025</v>
       </c>
       <c r="J28" t="n">
-        <v>47732697</v>
+        <v>38571428.57142857</v>
       </c>
       <c r="K28" t="n">
-        <v>47732697</v>
+        <v>53571428.57142857</v>
       </c>
       <c r="L28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2018-08</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2020-03</t>
-        </is>
-      </c>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2020/03/03/a-commercial-bifacial-hjt-solar-cell-with-24-1-efficiency/</t>
+          <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2020/03/03/a-commercial-bifacial-hjt-solar-cell-with-24-1-efficiency/</t>
+          <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://bbj.hu/business/industry/pharma/ecosolifer-building-huf-15-bln-solar-panel-plant/</t>
+          <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://bbj.hu/economy/environment/recycling/construction-of-ecosolifer-solar-panel-plant-delayed63459/</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine.com/2018/08/21/hungary-ecosolifers-100-mw-hjt-cell-production-line-back-on-track/</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine.com/2020/03/03/a-commercial-bifacial-hjt-solar-cell-with-24-1-efficiency/</t>
-        </is>
-      </c>
+          <t>https://www.pv-magazine.com/2024/09/30/dracula-technologies-relaunches-production-of-organic-photovoltaic-modules-in-france/</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>52c9d91f-5d8d-50b6-92bc-d5b2e7cb60be</t>
+          <t>ab958d6c-804b-53ec-8cc8-6b601343ee48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>enel</t>
+          <t>ecosolifer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Győr-Moson-Sopron</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -18398,7 +18374,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>cell, module</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -18410,68 +18386,68 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J29" t="n">
-        <v>80000000</v>
+        <v>47732697</v>
       </c>
       <c r="K29" t="n">
-        <v>80000000</v>
+        <v>47732697</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2014-09</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2020-03</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.pv-tech.org/enels-3sun-secures-e560-million-financing-for-3gw-heterojunction-module-plant-in-italy/</t>
+          <t>https://www.pv-magazine.com/2020/03/03/a-commercial-bifacial-hjt-solar-cell-with-24-1-efficiency/</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.pv-tech.org/enels-3sun-secures-e560-million-financing-for-3gw-heterojunction-module-plant-in-italy/</t>
+          <t>https://www.pv-magazine.com/2020/03/03/a-commercial-bifacial-hjt-solar-cell-with-24-1-efficiency/</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2022/10/08/the-weekend-read-catalyst-for-an-eu-solar-cell-module-comeback/</t>
+          <t>https://bbj.hu/business/industry/pharma/ecosolifer-building-huf-15-bln-solar-panel-plant/</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.pv-tech.org/enel-signs-grant-agreement-with-eu-for-3gw-bifacial-pv-module-facility-in-italy/</t>
+          <t>https://bbj.hu/business/industry/pharma/ecosolifer-building-huf-15-bln-solar-panel-plant/</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/01/24/enel-secures-e560-million-for-3-gw-heterojunction-panel-factory-in-italy/</t>
+          <t>https://www.pv-magazine.com/2018/08/21/hungary-ecosolifers-100-mw-hjt-cell-production-line-back-on-track/</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://www.pv-tech.org/3sun-set-to-reach-3gw-of-module-capacity-at-italian-plant-in-2023/</t>
+          <t>https://www.pv-magazine.com/2020/03/03/a-commercial-bifacial-hjt-solar-cell-with-24-1-efficiency/</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3bf36288-2164-5d1d-a088-66ae40fe28a1</t>
+          <t>52c9d91f-5d8d-50b6-92bc-d5b2e7cb60be</t>
         </is>
       </c>
     </row>
@@ -18502,7 +18478,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -18510,63 +18486,55 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
-        <v>480000000</v>
+        <v>80000000</v>
       </c>
       <c r="K30" t="n">
-        <v>560000000</v>
+        <v>80000000</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2021-05</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2022-09</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/11/19/3sun-earns-tuv-rheinland-certification-clearing-way-for-pv-module-sales/</t>
+          <t>https://www.pv-tech.org/enels-3sun-secures-e560-million-financing-for-3gw-heterojunction-module-plant-in-italy/</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/11/19/3sun-earns-tuv-rheinland-certification-clearing-way-for-pv-module-sales/</t>
+          <t>https://www.pv-tech.org/enels-3sun-secures-e560-million-financing-for-3gw-heterojunction-module-plant-in-italy/</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/06/15/eu-set-to-dig-into-raw-materials-supply/</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>https://www.pv-tech.org/3sun-set-to-reach-3gw-of-module-capacity-at-italian-plant-in-2023/</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine.com/2022/09/26/enel-unveils-680-w-n-type-heterojunction-solar-panel-for-utility-scale-applications/</t>
-        </is>
-      </c>
+          <t>https://www.pv-magazine.com/2022/10/08/the-weekend-read-catalyst-for-an-eu-solar-cell-module-comeback/</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2024/11/19/3sun-earns-tuv-rheinland-certification-clearing-way-for-pv-module-sales/</t>
+          <t>https://www.enel.com/es/medios/explora/busqueda-comunicados-de-prensa/press/2011/07/italys-largest-photovoltaic-panel-plant-opens-its-doors</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -18578,17 +18546,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>energetica</t>
+          <t>enel</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liebenfels</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -18598,11 +18566,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>cell, module</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -18610,60 +18578,68 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.55</v>
+        <v>2.8</v>
       </c>
       <c r="I31" t="n">
-        <v>0.55</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>45650000</v>
+        <v>480000000</v>
       </c>
       <c r="K31" t="n">
-        <v>45650000</v>
+        <v>560000000</v>
       </c>
       <c r="L31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2022-09</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2021/01/21/pv-magazine-award-the-winners/</t>
+          <t>https://www.pv-magazine.com/2024/11/19/3sun-earns-tuv-rheinland-certification-clearing-way-for-pv-module-sales/</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2021/01/21/pv-magazine-award-the-winners/</t>
+          <t>https://www.pv-magazine.com/2024/11/19/3sun-earns-tuv-rheinland-certification-clearing-way-for-pv-module-sales/</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2021/01/21/pv-magazine-award-the-winners/</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+          <t>https://www.pv-magazine.com/2024/06/15/eu-set-to-dig-into-raw-materials-supply/</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>https://www.enel.com/es/medios/explora/busqueda-comunicados-de-prensa/press/2011/07/italys-largest-photovoltaic-panel-plant-opens-its-doors</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2022/09/26/enel-unveils-680-w-n-type-heterojunction-solar-panel-for-utility-scale-applications/</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2021/01/21/pv-magazine-award-the-winners/</t>
+          <t>https://www.pv-magazine.com/2024/11/19/3sun-earns-tuv-rheinland-certification-clearing-way-for-pv-module-sales/</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>57d53335-c4f6-522b-9e5b-dcb625db2c71</t>
+          <t>3bf36288-2164-5d1d-a088-66ae40fe28a1</t>
         </is>
       </c>
     </row>
@@ -18694,35 +18670,43 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="J32" t="n">
-        <v>37350000</v>
+        <v>45650000</v>
       </c>
       <c r="K32" t="n">
-        <v>83000000</v>
+        <v>45650000</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>2021-01</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>https://www.pv-magazine.com/2021/01/21/pv-magazine-award-the-winners/</t>
@@ -18738,13 +18722,13 @@
           <t>https://www.pv-magazine.com/2021/01/21/pv-magazine-award-the-winners/</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
         <is>
           <t>https://www.pv-magazine.com/2021/01/21/pv-magazine-award-the-winners/</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>57d53335-c4f6-522b-9e5b-dcb625db2c71</t>
@@ -18754,7 +18738,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>energetica photovoltaic industries</t>
+          <t>energetica</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -18778,21 +18762,21 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>83000000</v>
+        <v>37350000</v>
       </c>
       <c r="K33" t="n">
         <v>83000000</v>
@@ -18802,17 +18786,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2016-11</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -18830,16 +18814,20 @@
           <t>https://www.pv-magazine.com/2019/11/11/energetica-begins-manufacturing-at-gigafactory-in-austria/</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>https://www.pv-magazine.com/2019/11/11/energetica-begins-manufacturing-at-gigafactory-in-austria/</t>
         </is>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2019/11/11/energetica-begins-manufacturing-at-gigafactory-in-austria/</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>4d4e740f-b470-5737-907c-45d10c7a6cce</t>
+          <t>57d53335-c4f6-522b-9e5b-dcb625db2c71</t>
         </is>
       </c>
     </row>
@@ -24490,7 +24478,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>solitik</t>
+          <t>solitek</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -24528,17 +24516,17 @@
         <v>0.6</v>
       </c>
       <c r="J97" t="n">
-        <v>49800000</v>
+        <v>50000000</v>
       </c>
       <c r="K97" t="n">
-        <v>49800000</v>
+        <v>50000000</v>
       </c>
       <c r="L97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -24555,19 +24543,19 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2023/12/04/solitek-launches-solar-carport-for-residential-commercial-applications/</t>
+          <t>https://www.pv-magazine.com/2023/03/20/solitek-to-build-600-mw-solar-module-factory-in-italy/</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://www.pv-magazine.com/2023/12/04/solitek-launches-solar-carport-for-residential-commercial-applications/</t>
+          <t>https://www.pv-magazine.com/2023/03/20/solitek-to-build-600-mw-solar-module-factory-in-italy/</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>90808f0a-d86b-5ae8-8f5d-d87d9cbcefcc</t>
+          <t>269a0052-7dcd-517c-88e4-2b63a9f847cc</t>
         </is>
       </c>
     </row>
